--- a/rules/CORE-000738/positive/01/data/unit-test-coreid-FB1106-positive.xlsx
+++ b/rules/CORE-000738/positive/01/data/unit-test-coreid-FB1106-positive.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000738\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B9D7BC-1555-4E98-ACED-B0240E779189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DA0594-47CE-484E-A6D2-23C5D6C3BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="74">
   <si>
     <t>Product</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>TEST</t>
+  </si>
+  <si>
+    <t>CURTRT</t>
   </si>
 </sst>
 </file>
@@ -344,7 +347,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -368,10 +371,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -952,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="7" t="s">
         <v>69</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>68</v>
       </c>
       <c r="H5" s="7"/>
@@ -1014,7 +1014,9 @@
       <c r="D7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="F7" s="7" t="s">
         <v>71</v>
       </c>
@@ -1262,25 +1264,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d36826f407302d9fd93d8089214679b0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="257daeb82d9c284d9d656fb5e9ad601e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1520,26 +1503,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BB30A1-25F5-4D6B-AA9C-850DE868D543}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DFFF2B-AFAE-466C-A5DC-966DF9457202}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{584BC493-59AD-414D-BB3D-0A3F4E45926F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1557,4 +1540,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DFFF2B-AFAE-466C-A5DC-966DF9457202}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BB30A1-25F5-4D6B-AA9C-850DE868D543}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>